--- a/files/港岛-寿臣山及浅水湾-No.3 Repulse Bay Road.xlsx
+++ b/files/港岛-寿臣山及浅水湾-No.3 Repulse Bay Road.xlsx
@@ -894,7 +894,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>1999-06-10</t>
+          <t>1999-06-11</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -960,7 +960,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>1997-06-26</t>
+          <t>1997-06-27</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1997-07-07</t>
+          <t>1997-07-08</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>1997-06-26</t>
+          <t>1997-06-27</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1997-12-15</t>
+          <t>1997-12-16</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1997-07-07</t>
+          <t>1997-07-08</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1997-12-15</t>
+          <t>1997-12-16</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1997-07-18</t>
+          <t>1997-07-19</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1997-10-21</t>
+          <t>1997-10-22</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1999-03-10</t>
+          <t>1999-03-11</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1997-07-03</t>
+          <t>1997-07-04</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1997-06-24</t>
+          <t>1997-06-25</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1997-06-24</t>
+          <t>1997-06-25</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1997-07-11</t>
+          <t>1997-07-12</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1997-07-11</t>
+          <t>1997-07-12</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1997-06-24</t>
+          <t>1997-06-25</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1997-06-25</t>
+          <t>1997-06-26</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1997-06-26</t>
+          <t>1997-06-27</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1997-07-07</t>
+          <t>1997-07-08</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1997-07-03</t>
+          <t>1997-07-04</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1997-07-06</t>
+          <t>1997-07-07</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1997-07-06</t>
+          <t>1997-07-07</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1997-07-10</t>
+          <t>1997-07-11</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1997-06-26</t>
+          <t>1997-06-27</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1997-07-16</t>
+          <t>1997-07-17</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1997-06-26</t>
+          <t>1997-06-27</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1997-07-06</t>
+          <t>1997-07-07</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1997-07-06</t>
+          <t>1997-07-07</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1997-07-04</t>
+          <t>1997-07-05</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>1997-07-06</t>
+          <t>1997-07-07</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3688,7 +3688,7 @@
           <t>A | 1709呎 (4+房)
 $5157万
 $30,176/呎
-(97年-06月-26日)</t>
+(97年-06月-27日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -3696,7 +3696,7 @@
           <t>B | 1632呎 (4+房)
 $2830万
 $17,341/呎
-(99年-06月-10日)</t>
+(99年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
           <t>A | 1709呎 (4+房)
 $5193万
 $30,386/呎
-(97年-06月-26日)</t>
+(97年-06月-27日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -3719,7 +3719,7 @@
           <t>B | 1632呎 (4+房)
 $5654万
 $34,645/呎
-(97年-07月-07日)</t>
+(97年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3734,7 @@
           <t>A | 1741呎 (4+房)
 $5750万
 $33,027/呎
-(97年-07月-07日)</t>
+(97年-07月-08日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -3742,7 +3742,7 @@
           <t>B | 1682呎 (4+房)
 $4987万
 $29,650/呎
-(97年-12月-15日)</t>
+(97年-12月-16日)</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3757,7 @@
           <t>A | 1741呎 (4+房)
 $5168万
 $29,685/呎
-(97年-07月-18日)</t>
+(97年-07月-19日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -3765,7 +3765,7 @@
           <t>B | 1682呎 (4+房)
 $4987万
 $29,650/呎
-(97年-12月-15日)</t>
+(97年-12月-16日)</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
           <t>A | 1741呎 (4+房)
 $5854万
 $33,627/呎
-(97年-10月-21日)</t>
+(97年-10月-22日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -3826,7 +3826,7 @@
           <t>A | 1741呎 (4+房)
 $2359万
 $13,551/呎
-(99年-03月-10日)</t>
+(99年-03月-11日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -3880,7 +3880,7 @@
           <t>B | 1671呎 (4+房)
 $5200万
 $31,119/呎
-(97年-07月-03日)</t>
+(97年-07月-04日)</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3895,7 @@
           <t>A | 1741呎 (4+房)
 $5180万
 $29,753/呎
-(97年-06月-24日)</t>
+(97年-06月-25日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -3903,7 +3903,7 @@
           <t>B | 1671呎 (4+房)
 $4700万
 $28,127/呎
-(97年-06月-24日)</t>
+(97年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
           <t>A | 1741呎 (4+房)
 $5200万
 $29,868/呎
-(97年-07月-11日)</t>
+(97年-07月-12日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -3926,7 +3926,7 @@
           <t>B | 1671呎 (4+房)
 $5400万
 $32,316/呎
-(97年-07月-11日)</t>
+(97年-07月-12日)</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
           <t>A | 1796呎 (4+房)
 $4800万
 $26,726/呎
-(97年-06月-25日)</t>
+(97年-06月-26日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -3949,7 +3949,7 @@
           <t>B | 1671呎 (4+房)
 $4670万
 $27,947/呎
-(97年-06月-24日)</t>
+(97年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
           <t>A | 1734呎 (4+房)
 $4800万
 $27,682/呎
-(97年-06月-26日)</t>
+(97年-06月-27日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -3987,7 +3987,7 @@
           <t>A | 1734呎 (4+房)
 $4780万
 $27,566/呎
-(97年-07月-03日)</t>
+(97年-07月-04日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -3995,7 +3995,7 @@
           <t>B | 1664呎 (4+房)
 $5020万
 $30,168/呎
-(97年-07月-07日)</t>
+(97年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
           <t>A | 1734呎 (4+房)
 $5331万
 $30,744/呎
-(97年-07月-06日)</t>
+(97年-07月-07日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -4018,7 +4018,7 @@
           <t>B | 1664呎 (4+房)
 $5000万
 $30,048/呎
-(97年-07月-06日)</t>
+(97年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4033,7 @@
           <t>A | 1734呎 (4+房)
 $4760万
 $27,451/呎
-(97年-06月-26日)</t>
+(97年-06月-27日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -4041,7 +4041,7 @@
           <t>B | 1664呎 (4+房)
 $4850万
 $29,147/呎
-(97年-07月-10日)</t>
+(97年-07月-11日)</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
           <t>A | 1734呎 (4+房)
 $4760万
 $27,451/呎
-(97年-06月-26日)</t>
+(97年-06月-27日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -4064,7 +4064,7 @@
           <t>B | 1659呎 (4+房)
 $4750万
 $28,632/呎
-(97年-07月-16日)</t>
+(97年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
           <t>A | 1734呎 (4+房)
 $4860万
 $28,028/呎
-(97年-07月-06日)</t>
+(97年-07月-07日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -4087,7 +4087,7 @@
           <t>B | 1659呎 (4+房)
 $4750万
 $28,632/呎
-(97年-07月-06日)</t>
+(97年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -4110,7 +4110,7 @@
           <t>B | 1659呎 (4+房)
 $4700万
 $28,330/呎
-(97年-07月-04日)</t>
+(97年-07月-05日)</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
           <t>B | 1659呎 (4+房)
 $4720万
 $28,451/呎
-(97年-07月-06日)</t>
+(97年-07月-07日)</t>
         </is>
       </c>
     </row>
